--- a/output/pdf_financials_xlsx/GX.xlsx
+++ b/output/pdf_financials_xlsx/GX.xlsx
@@ -1113,22 +1113,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.019922</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.011959</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006546</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005348</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002751</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00142</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.596672</v>
+        <v>-2.616594</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.299832</v>
+        <v>-2.311791</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.776461</v>
+        <v>-1.783007</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.272048</v>
+        <v>-1.277396</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.157137</v>
+        <v>-3.154386</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.837466</v>
+        <v>-1.836046</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -2315,22 +2315,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.596672</v>
+        <v>-2.616594</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.299832</v>
+        <v>-2.311791</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.776461</v>
+        <v>-1.783007</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.272048</v>
+        <v>-1.277396</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.157137</v>
+        <v>-3.154386</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.837466</v>
+        <v>-1.836046</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2385,22 +2385,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-41.24164302556543</v>
+        <v>-41.55805419045468</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-79.20516290076006</v>
+        <v>-79.61702539468577</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-129.9552516900406</v>
+        <v>-130.4341178613571</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-176.2962552318652</v>
+        <v>-177.0374476813482</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-492.3333749181299</v>
+        <v>-491.904375760222</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-428.2808082361963</v>
+        <v>-427.9498313649532</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -2602,43 +2602,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.693056</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.264214</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.264214</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000396</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.06665699999999999</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.015667</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.006715</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.008416999999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.007777</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.009513000000000001</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0</v>
@@ -2706,43 +2706,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.693056</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.264214</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.264214</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000396</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.06665699999999999</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.015667</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.006715</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.008416999999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.007777</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.009513000000000001</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0</v>
@@ -3330,43 +3330,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.193647</v>
+        <v>0.500591</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.335246</v>
+        <v>0.071032</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.335246</v>
+        <v>0.071032</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.020484</v>
+        <v>0.020088</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.069831</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.07606499999999999</v>
+        <v>0.009408</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.011336</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.018702</v>
+        <v>0.003035</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.00975</v>
+        <v>0.003035</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.012979</v>
+        <v>0.004562</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.008544</v>
+        <v>0.000767</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.054534</v>
+        <v>0.045021</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.020316</v>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -44156,7 +44156,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -45782,7 +45782,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E423" s="5" t="n">
@@ -45871,7 +45871,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E424" s="5" t="n">
@@ -47675,7 +47675,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">

--- a/output/pdf_financials_xlsx/GX.xlsx
+++ b/output/pdf_financials_xlsx/GX.xlsx
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.580882</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -40279,7 +40279,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GX.xlsx
+++ b/output/pdf_financials_xlsx/GX.xlsx
@@ -1405,10 +1405,10 @@
         <v>-1.272048</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-3.157137</v>
+        <v>-2.950887</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-1.837466</v>
+        <v>-1.16095</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.694</v>
+        <v>-0.694</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1475,10 +1475,10 @@
         <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.20625</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.676516</v>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
@@ -1927,15 +1927,11 @@
       <c r="H23" s="3" t="n">
         <v>-0.465021</v>
       </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="3" t="n">
+        <v>1.709145</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>-0.337383</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.731952</v>
@@ -1943,10 +1939,8 @@
       <c r="L23" s="3" t="n">
         <v>0.806854</v>
       </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M23" s="3" t="n">
+        <v>-0.084158</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-0.155613</v>
@@ -2187,10 +2181,10 @@
         <v>-1.277396</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.154386</v>
+        <v>-2.948136</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.836046</v>
+        <v>-1.15953</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -2327,10 +2321,10 @@
         <v>-1.277396</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.154386</v>
+        <v>-2.948136</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.836046</v>
+        <v>-1.15953</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2397,10 +2391,10 @@
         <v>-177.0374476813482</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-491.904375760222</v>
+        <v>-459.7411346411752</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-427.9498313649532</v>
+        <v>-270.2659236002825</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -2467,10 +2461,10 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-6.989423857978974</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-58.27262155992937</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -6079,15 +6073,11 @@
       <c r="H99" s="3" t="n">
         <v>-0.465021</v>
       </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="3" t="n">
+        <v>1.709145</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>-0.337383</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-0.731952</v>
@@ -6095,10 +6085,8 @@
       <c r="L99" s="3" t="n">
         <v>0.806854</v>
       </c>
-      <c r="M99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M99" s="3" t="n">
+        <v>-0.084158</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>-0.155613</v>
@@ -6646,31 +6634,31 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.053242</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.025838</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.020013</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.024731</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.010309</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.013336</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.0144</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.006027</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.009960999999999999</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -29829,7 +29817,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -30282,7 +30274,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -30371,7 +30367,11 @@
           <t>Accretion 5</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -32984,7 +32984,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -33769,7 +33773,11 @@
           <t>Accretion 6</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -34738,7 +34746,11 @@
           <t>Accretion 7</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -36819,7 +36831,11 @@
           <t>Accretion 8</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -41383,7 +41399,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E374" s="5" t="n">
         <v>-0.694</v>
       </c>
@@ -44607,7 +44627,11 @@
           <t>Income tax recovery 10a</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -47952,7 +47976,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -48951,7 +48979,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E458" s="5" t="n">
         <v>0.694</v>
       </c>
